--- a/2026_연간_일별공급계획_2.xlsx
+++ b/2026_연간_일별공급계획_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\일일예측_관리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7A18C8-59B2-4CCE-8607-9A7B1DE87886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C628A33-9D6B-4655-821B-116174868621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -122,7 +122,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -175,6 +175,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -182,7 +208,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -231,6 +257,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -1553,37 +1600,37 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="6">
-        <v>2026</v>
-      </c>
-      <c r="B61" s="6">
+      <c r="A61" s="20">
+        <v>2026</v>
+      </c>
+      <c r="B61" s="20">
         <v>2</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61" s="20">
         <v>28</v>
       </c>
-      <c r="D61" s="15">
+      <c r="D61" s="21">
         <v>177297.31779130435</v>
       </c>
-      <c r="E61" s="16">
+      <c r="E61" s="22">
         <v>4165525.8141649901</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="6">
-        <v>2026</v>
-      </c>
-      <c r="B62" s="6">
+      <c r="A62" s="26">
+        <v>2026</v>
+      </c>
+      <c r="B62" s="26">
         <v>3</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="26">
         <v>1</v>
       </c>
-      <c r="D62" s="7">
-        <v>159695.19099999999</v>
-      </c>
-      <c r="E62" s="10">
-        <v>3751972</v>
+      <c r="D62" s="27">
+        <v>154571.64350313091</v>
+      </c>
+      <c r="E62" s="28">
+        <v>3631596.5393212629</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -1597,10 +1644,10 @@
         <v>2</v>
       </c>
       <c r="D63" s="7">
-        <v>188111.432</v>
+        <v>164267.48195548551</v>
       </c>
       <c r="E63" s="10">
-        <v>4419600</v>
+        <v>3859396.235121714</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -1614,10 +1661,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="7">
-        <v>189358.38800000001</v>
+        <v>190296.90896154233</v>
       </c>
       <c r="E64" s="10">
-        <v>4448897</v>
+        <v>4470946.8073571492</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -1631,10 +1678,10 @@
         <v>4</v>
       </c>
       <c r="D65" s="7">
-        <v>194136.929</v>
+        <v>195099.60506060976</v>
       </c>
       <c r="E65" s="10">
-        <v>4561166</v>
+        <v>4583784.1566762151</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -1648,10 +1695,10 @@
         <v>5</v>
       </c>
       <c r="D66" s="7">
-        <v>198296.981</v>
+        <v>199280.23192232152</v>
       </c>
       <c r="E66" s="10">
-        <v>4658905</v>
+        <v>4682006.2477344526</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -1665,10 +1712,10 @@
         <v>6</v>
       </c>
       <c r="D67" s="7">
-        <v>199049.80300000001</v>
+        <v>190296.90896154233</v>
       </c>
       <c r="E67" s="10">
-        <v>4676592</v>
+        <v>4470946.8073571492</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -1682,10 +1729,10 @@
         <v>7</v>
       </c>
       <c r="D68" s="7">
-        <v>174852.40100000001</v>
+        <v>163219.31036491692</v>
       </c>
       <c r="E68" s="10">
-        <v>4108085</v>
+        <v>3834769.8791184109</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -1699,10 +1746,10 @@
         <v>8</v>
       </c>
       <c r="D69" s="7">
-        <v>143606.427</v>
+        <v>156817.72548292077</v>
       </c>
       <c r="E69" s="10">
-        <v>3373973</v>
+        <v>3684367.3021854842</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -1716,10 +1763,10 @@
         <v>9</v>
       </c>
       <c r="D70" s="7">
-        <v>171443.519</v>
+        <v>172294.08453829604</v>
       </c>
       <c r="E70" s="10">
-        <v>4027994</v>
+        <v>4047977.9277376132</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -1733,10 +1780,10 @@
         <v>10</v>
       </c>
       <c r="D71" s="7">
-        <v>166186.15299999999</v>
+        <v>170079.15626829298</v>
       </c>
       <c r="E71" s="10">
-        <v>3904475</v>
+        <v>3995939.1083404124</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -1750,10 +1797,10 @@
         <v>11</v>
       </c>
       <c r="D72" s="7">
-        <v>154411.75</v>
+        <v>169819.87700619645</v>
       </c>
       <c r="E72" s="10">
-        <v>3627840</v>
+        <v>3989847.4498084355</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -1767,10 +1814,10 @@
         <v>12</v>
       </c>
       <c r="D73" s="7">
-        <v>146642.70699999999</v>
+        <v>164396.67678052888</v>
       </c>
       <c r="E73" s="10">
-        <v>3445309</v>
+        <v>3862431.613855435</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -1784,10 +1831,10 @@
         <v>13</v>
       </c>
       <c r="D74" s="7">
-        <v>155373.92000000001</v>
+        <v>158204.55659941444</v>
       </c>
       <c r="E74" s="10">
-        <v>3650446</v>
+        <v>3716950.3230367792</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -1801,10 +1848,10 @@
         <v>14</v>
       </c>
       <c r="D75" s="7">
-        <v>148331.59700000001</v>
+        <v>143277.67045662727</v>
       </c>
       <c r="E75" s="10">
-        <v>3484989</v>
+        <v>3366249.3352589635</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -1818,10 +1865,10 @@
         <v>15</v>
       </c>
       <c r="D76" s="7">
-        <v>129048.149</v>
+        <v>140802.55997254423</v>
       </c>
       <c r="E76" s="10">
-        <v>3031933</v>
+        <v>3308097.6428481126</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -1835,10 +1882,10 @@
         <v>16</v>
       </c>
       <c r="D77" s="7">
-        <v>153397.92300000001</v>
+        <v>160483.15442333318</v>
       </c>
       <c r="E77" s="10">
-        <v>3604020</v>
+        <v>3770485.0321484189</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -1852,10 +1899,10 @@
         <v>17</v>
       </c>
       <c r="D78" s="7">
-        <v>159059.21299999999</v>
+        <v>166144.05181694173</v>
       </c>
       <c r="E78" s="10">
-        <v>3737030</v>
+        <v>3903485.4642986096</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -1869,10 +1916,10 @@
         <v>18</v>
       </c>
       <c r="D79" s="7">
-        <v>165927.908</v>
+        <v>161845.96874830086</v>
       </c>
       <c r="E79" s="10">
-        <v>3898407</v>
+        <v>3802503.7884618295</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -1886,10 +1933,10 @@
         <v>19</v>
       </c>
       <c r="D80" s="7">
-        <v>161368.375</v>
+        <v>153712.11014991064</v>
       </c>
       <c r="E80" s="10">
-        <v>3791283</v>
+        <v>3611402.1603249446</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -1903,10 +1950,10 @@
         <v>20</v>
       </c>
       <c r="D81" s="7">
-        <v>150217.617</v>
+        <v>153660.72659390385</v>
       </c>
       <c r="E81" s="10">
-        <v>3529300</v>
+        <v>3610194.9250265216</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -1920,10 +1967,10 @@
         <v>21</v>
       </c>
       <c r="D82" s="7">
-        <v>133062.11499999999</v>
+        <v>124137.97659596184</v>
       </c>
       <c r="E82" s="10">
-        <v>3126239</v>
+        <v>2916570.1805784795</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -1937,10 +1984,10 @@
         <v>22</v>
       </c>
       <c r="D83" s="7">
-        <v>105504.579</v>
+        <v>119182.32394505019</v>
       </c>
       <c r="E83" s="10">
-        <v>2478786</v>
+        <v>2800139.1806275449</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -1954,10 +2001,10 @@
         <v>23</v>
       </c>
       <c r="D84" s="7">
-        <v>128294.489</v>
+        <v>130520.76865967279</v>
       </c>
       <c r="E84" s="10">
-        <v>3014226</v>
+        <v>3066531.2280542441</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -1971,10 +2018,10 @@
         <v>24</v>
       </c>
       <c r="D85" s="7">
-        <v>130304.88100000001</v>
+        <v>135563.17480094431</v>
       </c>
       <c r="E85" s="10">
-        <v>3061459</v>
+        <v>3185000.4652149593</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -1988,10 +2035,10 @@
         <v>25</v>
       </c>
       <c r="D86" s="7">
-        <v>121962.899</v>
+        <v>127154.24603455765</v>
       </c>
       <c r="E86" s="10">
-        <v>2865468</v>
+        <v>2987436.1777731278</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -2005,10 +2052,10 @@
         <v>26</v>
       </c>
       <c r="D87" s="7">
-        <v>122938.026</v>
+        <v>128214.91716029312</v>
       </c>
       <c r="E87" s="10">
-        <v>2888378</v>
+        <v>3012356.205161598</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -2022,10 +2069,10 @@
         <v>27</v>
       </c>
       <c r="D88" s="7">
-        <v>128132.78</v>
+        <v>130150.9880887076</v>
       </c>
       <c r="E88" s="10">
-        <v>3010426</v>
+        <v>3057843.3871838823</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -2039,10 +2086,10 @@
         <v>28</v>
       </c>
       <c r="D89" s="7">
-        <v>115031.80900000001</v>
+        <v>118012.13759255769</v>
       </c>
       <c r="E89" s="10">
-        <v>2702625</v>
+        <v>2772646.1384901837</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -2056,10 +2103,10 @@
         <v>29</v>
       </c>
       <c r="D90" s="7">
-        <v>112061.109</v>
+        <v>115399.7129147677</v>
       </c>
       <c r="E90" s="10">
-        <v>2632829</v>
+        <v>2711268.3061524727</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -2073,43 +2120,43 @@
         <v>30</v>
       </c>
       <c r="D91" s="7">
-        <v>142970.18400000001</v>
+        <v>124284.22963269848</v>
       </c>
       <c r="E91" s="10">
-        <v>3359025</v>
+        <v>2920006.3349082181</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="6">
-        <v>2026</v>
-      </c>
-      <c r="B92" s="6">
+      <c r="A92" s="8">
+        <v>2026</v>
+      </c>
+      <c r="B92" s="8">
         <v>3</v>
       </c>
-      <c r="C92" s="6">
+      <c r="C92" s="8">
         <v>31</v>
       </c>
-      <c r="D92" s="7">
-        <v>161227.15900000001</v>
-      </c>
-      <c r="E92" s="10">
-        <v>3787965</v>
+      <c r="D92" s="9">
+        <v>128815.11500802798</v>
+      </c>
+      <c r="E92" s="11">
+        <v>3026457.6042108866</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="6">
-        <v>2026</v>
-      </c>
-      <c r="B93" s="6">
+      <c r="A93" s="23">
+        <v>2026</v>
+      </c>
+      <c r="B93" s="23">
         <v>4</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C93" s="23">
         <v>1</v>
       </c>
-      <c r="D93" s="7">
+      <c r="D93" s="24">
         <v>129696.34300000001</v>
       </c>
-      <c r="E93" s="10">
+      <c r="E93" s="25">
         <v>3047162</v>
       </c>
     </row>

--- a/2026_연간_일별공급계획_2.xlsx
+++ b/2026_연간_일별공급계획_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\일일예측_관리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C628A33-9D6B-4655-821B-116174868621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2C8560-D94D-4AD5-8420-FB41CB8A18B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2154,10 +2154,10 @@
         <v>1</v>
       </c>
       <c r="D93" s="24">
-        <v>129696.34300000001</v>
+        <v>135678.90173531568</v>
       </c>
       <c r="E93" s="25">
-        <v>3047162</v>
+        <v>3187719.4214532734</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -2171,10 +2171,10 @@
         <v>2</v>
       </c>
       <c r="D94" s="7">
-        <v>128508.93800000001</v>
+        <v>134504.05417219922</v>
       </c>
       <c r="E94" s="10">
-        <v>3019264</v>
+        <v>3160116.8661090434</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -2188,10 +2188,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="7">
-        <v>122612.189</v>
+        <v>128459.71513042593</v>
       </c>
       <c r="E95" s="10">
-        <v>2880722</v>
+        <v>3018107.6317558894</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -2205,10 +2205,10 @@
         <v>4</v>
       </c>
       <c r="D96" s="7">
-        <v>104394.21</v>
+        <v>101219.22966547139</v>
       </c>
       <c r="E96" s="10">
-        <v>2452699</v>
+        <v>2378103.7442255332</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -2222,10 +2222,10 @@
         <v>5</v>
       </c>
       <c r="D97" s="7">
-        <v>93045.054000000004</v>
+        <v>97257.943587270536</v>
       </c>
       <c r="E97" s="10">
-        <v>2186055</v>
+        <v>2285034.9737394103</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -2239,10 +2239,10 @@
         <v>6</v>
       </c>
       <c r="D98" s="7">
-        <v>115057.524</v>
+        <v>113315.63602285007</v>
       </c>
       <c r="E98" s="10">
-        <v>2703229</v>
+        <v>2662303.7855144152</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -2256,10 +2256,10 @@
         <v>7</v>
       </c>
       <c r="D99" s="7">
-        <v>124353.235</v>
+        <v>116899.26933336745</v>
       </c>
       <c r="E99" s="10">
-        <v>2921628</v>
+        <v>2746499.7611391922</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -2273,10 +2273,10 @@
         <v>8</v>
       </c>
       <c r="D100" s="7">
-        <v>108045.76700000001</v>
+        <v>116691.17527400244</v>
       </c>
       <c r="E100" s="10">
-        <v>2538490</v>
+        <v>2741610.6776778526</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -2290,10 +2290,10 @@
         <v>9</v>
       </c>
       <c r="D101" s="7">
-        <v>106882.639</v>
+        <v>116292.53689176546</v>
       </c>
       <c r="E101" s="10">
-        <v>2511163</v>
+        <v>2732244.8345221304</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -2307,10 +2307,10 @@
         <v>10</v>
       </c>
       <c r="D102" s="7">
-        <v>101335.49400000001</v>
+        <v>101862.72974592153</v>
       </c>
       <c r="E102" s="10">
-        <v>2380835</v>
+        <v>2393222.5112403147</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -2324,10 +2324,10 @@
         <v>11</v>
       </c>
       <c r="D103" s="7">
-        <v>92335.354000000007</v>
+        <v>92627.663038175349</v>
       </c>
       <c r="E103" s="10">
-        <v>2169381</v>
+        <v>2176248.4561279831</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -2341,10 +2341,10 @@
         <v>12</v>
       </c>
       <c r="D104" s="7">
-        <v>89099.184000000008</v>
+        <v>89381.248189381338</v>
       </c>
       <c r="E104" s="10">
-        <v>2093348</v>
+        <v>2099975.2881465433</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -2358,10 +2358,10 @@
         <v>13</v>
       </c>
       <c r="D105" s="7">
-        <v>118116.048</v>
+        <v>101656.29507457175</v>
       </c>
       <c r="E105" s="10">
-        <v>2775087</v>
+        <v>2388372.4144109143</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -2375,10 +2375,10 @@
         <v>14</v>
       </c>
       <c r="D106" s="7">
-        <v>110548.27100000001</v>
+        <v>108240.31815658823</v>
       </c>
       <c r="E106" s="10">
-        <v>2597286</v>
+        <v>2543061.301049931</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -2392,10 +2392,10 @@
         <v>15</v>
       </c>
       <c r="D107" s="7">
-        <v>104559.25900000001</v>
+        <v>109247.9179510893</v>
       </c>
       <c r="E107" s="10">
-        <v>2456576</v>
+        <v>2566734.4395622793</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
@@ -2409,10 +2409,10 @@
         <v>16</v>
       </c>
       <c r="D108" s="7">
-        <v>95786.82</v>
+        <v>103329.35327644064</v>
       </c>
       <c r="E108" s="10">
-        <v>2250472</v>
+        <v>2427680.2217052518</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -2426,10 +2426,10 @@
         <v>17</v>
       </c>
       <c r="D109" s="7">
-        <v>89922.281000000003</v>
+        <v>91322.600432160427</v>
       </c>
       <c r="E109" s="10">
-        <v>2112687</v>
+        <v>2145586.552455429</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -2443,10 +2443,10 @@
         <v>18</v>
       </c>
       <c r="D110" s="7">
-        <v>81997.933000000005</v>
+        <v>80612.366197197451</v>
       </c>
       <c r="E110" s="10">
-        <v>1926507</v>
+        <v>1893954.0492257935</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
@@ -2460,10 +2460,10 @@
         <v>19</v>
       </c>
       <c r="D111" s="7">
-        <v>77974.907999999996</v>
+        <v>79866.906037006585</v>
       </c>
       <c r="E111" s="10">
-        <v>1831988</v>
+        <v>1876439.7725020929</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
@@ -2480,7 +2480,7 @@
         <v>96457.057000000001</v>
       </c>
       <c r="E112" s="10">
-        <v>2266218</v>
+        <v>2266218.4761412498</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -2494,10 +2494,10 @@
         <v>21</v>
       </c>
       <c r="D113" s="7">
-        <v>113133.476</v>
+        <v>104147.77765926988</v>
       </c>
       <c r="E113" s="10">
-        <v>2658024</v>
+        <v>2446908.7625230802</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -2511,10 +2511,10 @@
         <v>22</v>
       </c>
       <c r="D114" s="7">
-        <v>103636.268</v>
+        <v>102279.695613444</v>
       </c>
       <c r="E114" s="10">
-        <v>2434891</v>
+        <v>2403018.9510477171</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -2528,10 +2528,10 @@
         <v>23</v>
       </c>
       <c r="D115" s="7">
-        <v>98896.760999999999</v>
+        <v>97429.388701657328</v>
       </c>
       <c r="E115" s="10">
-        <v>2323538</v>
+        <v>2289063.0054661869</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -2548,7 +2548,7 @@
         <v>94178.402000000002</v>
       </c>
       <c r="E116" s="10">
-        <v>2212682</v>
+        <v>2212682.4237013366</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -2562,10 +2562,10 @@
         <v>25</v>
       </c>
       <c r="D117" s="7">
-        <v>76935.66</v>
+        <v>74356.377690000008</v>
       </c>
       <c r="E117" s="10">
-        <v>1807571</v>
+        <v>1746972.1986232176</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -2579,10 +2579,10 @@
         <v>26</v>
       </c>
       <c r="D118" s="7">
-        <v>68861.159</v>
+        <v>71440.441310000009</v>
       </c>
       <c r="E118" s="10">
-        <v>1617864</v>
+        <v>1678463.4849517187</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
@@ -2599,7 +2599,7 @@
         <v>93693.858999999997</v>
       </c>
       <c r="E119" s="10">
-        <v>2201298</v>
+        <v>2201298.2872447898</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -2613,10 +2613,10 @@
         <v>28</v>
       </c>
       <c r="D120" s="7">
-        <v>105791.07800000001</v>
+        <v>96738.638129286104</v>
       </c>
       <c r="E120" s="10">
-        <v>2485517</v>
+        <v>2272834.1077763806</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
@@ -2630,43 +2630,43 @@
         <v>29</v>
       </c>
       <c r="D121" s="7">
-        <v>81993.55</v>
+        <v>95681.813325015028</v>
       </c>
       <c r="E121" s="10">
-        <v>1926404</v>
+        <v>2248004.4481125632</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="6">
-        <v>2026</v>
-      </c>
-      <c r="B122" s="6">
+      <c r="A122" s="8">
+        <v>2026</v>
+      </c>
+      <c r="B122" s="8">
         <v>4</v>
       </c>
-      <c r="C122" s="6">
+      <c r="C122" s="8">
         <v>30</v>
       </c>
-      <c r="D122" s="7">
-        <v>107518.789</v>
-      </c>
-      <c r="E122" s="10">
-        <v>2526109</v>
+      <c r="D122" s="9">
+        <v>90498.199660127633</v>
+      </c>
+      <c r="E122" s="11">
+        <v>2126214.1518484787</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="6">
-        <v>2026</v>
-      </c>
-      <c r="B123" s="6">
+      <c r="A123" s="23">
+        <v>2026</v>
+      </c>
+      <c r="B123" s="23">
         <v>5</v>
       </c>
-      <c r="C123" s="6">
+      <c r="C123" s="23">
         <v>1</v>
       </c>
-      <c r="D123" s="7">
+      <c r="D123" s="24">
         <v>82016.81</v>
       </c>
-      <c r="E123" s="10">
+      <c r="E123" s="25">
         <v>1926951</v>
       </c>
     </row>
